--- a/files/option_2per_risk_neutral.xlsx
+++ b/files/option_2per_risk_neutral.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oyvind/Library/Mobile Documents/com~apple~CloudDocs/Documents/Teaching/SelFin_2023/S09_options/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oyvind/Projects/mst0037_files/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7797C993-742D-8D45-99B8-51B244B99EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A432F9F3-FA0E-F34B-A3D2-E4BB63BABAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6400" yWindow="1820" windowWidth="28040" windowHeight="17440" xr2:uid="{CF9F5530-3642-4842-8C3F-681478A13CA0}"/>
+    <workbookView xWindow="5440" yWindow="1820" windowWidth="28040" windowHeight="17440" xr2:uid="{CF9F5530-3642-4842-8C3F-681478A13CA0}"/>
   </bookViews>
   <sheets>
     <sheet name="call option" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -260,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -276,13 +276,12 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -301,9 +300,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -341,7 +340,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -447,7 +446,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -589,7 +588,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -597,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF7E594-CB62-9746-9919-5FB3D64B5837}">
-  <dimension ref="A2:E20"/>
+  <dimension ref="B2:D20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -605,14 +604,14 @@
     <col min="3" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B2" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="14"/>
     </row>
-    <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" ht="18" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
@@ -620,7 +619,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B5" s="6" t="s">
         <v>0</v>
       </c>
@@ -628,7 +627,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B6" s="6" t="s">
         <v>1</v>
       </c>
@@ -636,7 +635,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
@@ -644,7 +643,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
@@ -652,7 +651,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B10" s="8" t="s">
         <v>3</v>
       </c>
@@ -661,16 +660,16 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B11" s="17" t="s">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B11" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="17">
         <f>MAX(0,C6-C7)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B12" s="10" t="s">
         <v>9</v>
       </c>
@@ -679,51 +678,31 @@
         <v>0.46739130434782578</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B14" s="16" t="s">
+    <row r="14" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="18">
         <f>(C12*C10+(1-C12)*C11)/(1+C8)</f>
         <v>8.2887127864639059</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="15"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B17" s="19"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C19" s="20"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C20" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{9641a79b-5684-4ff8-89b0-3b715ae642f9}" enabled="1" method="Privileged" siteId="{adee44b2-91fc-40f1-abdd-9cc29351b5fd}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>